--- a/Cursor/3_쿠팡 모니터링/쿠팡 WAU 모니터링.xlsx
+++ b/Cursor/3_쿠팡 모니터링/쿠팡 WAU 모니터링.xlsx
@@ -8,31 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Cursor/3_쿠팡 모니터링/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D05725-61DC-2947-BF5D-B3C60490EF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E556EA60-470A-3346-8302-CA9AD65A1256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8160" yWindow="2320" windowWidth="27700" windowHeight="16880" xr2:uid="{557A2CCC-BB76-854E-B723-57C8CB621632}"/>
+    <workbookView xWindow="8160" yWindow="7200" windowWidth="27700" windowHeight="16880" xr2:uid="{557A2CCC-BB76-854E-B723-57C8CB621632}"/>
   </bookViews>
   <sheets>
     <sheet name="MI-INSIGHT1773654315714" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="47">
   <si>
     <t>모바일인덱스 INSIGHT CSV REPORT</t>
   </si>
@@ -173,10 +161,6 @@
   </si>
   <si>
     <t>2026-03-02 ~ 2026-03-08</t>
-  </si>
-  <si>
-    <t>WoW</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1128,35 +1112,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8398EB-50DF-6E4C-9081-89E2B7760E95}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1172,11 +1156,8 @@
       <c r="E7" t="s">
         <v>9</v>
       </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1192,12 +1173,8 @@
       <c r="E8">
         <v>8242690</v>
       </c>
-      <c r="F8" t="e">
-        <f t="shared" ref="F8:F42" si="0">(C8-C7)/C7</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1213,12 +1190,8 @@
       <c r="E9">
         <v>8266969</v>
       </c>
-      <c r="F9">
-        <f t="shared" si="0"/>
-        <v>2.6208453944768922E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1234,12 +1207,8 @@
       <c r="E10">
         <v>8261570</v>
       </c>
-      <c r="F10">
-        <f t="shared" si="0"/>
-        <v>-3.1110843010371289E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1255,12 +1224,8 @@
       <c r="E11">
         <v>8407703</v>
       </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
-        <v>1.1931353804096448E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1276,12 +1241,8 @@
       <c r="E12">
         <v>8228256</v>
       </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
-        <v>-1.0116090137822158E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1297,12 +1258,8 @@
       <c r="E13">
         <v>8193626</v>
       </c>
-      <c r="F13">
-        <f t="shared" si="0"/>
-        <v>-2.8909597118933392E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1318,12 +1275,8 @@
       <c r="E14">
         <v>8203443</v>
       </c>
-      <c r="F14">
-        <f t="shared" si="0"/>
-        <v>-4.6364698078313961E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1339,12 +1292,8 @@
       <c r="E15">
         <v>8348178</v>
       </c>
-      <c r="F15">
-        <f t="shared" si="0"/>
-        <v>9.0436592673034649E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -1360,12 +1309,8 @@
       <c r="E16">
         <v>8316055</v>
       </c>
-      <c r="F16">
-        <f t="shared" si="0"/>
-        <v>-9.9252822808878777E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1381,12 +1326,8 @@
       <c r="E17">
         <v>8559015</v>
       </c>
-      <c r="F17">
-        <f t="shared" si="0"/>
-        <v>1.5974646047414467E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -1402,12 +1343,8 @@
       <c r="E18">
         <v>8373883</v>
       </c>
-      <c r="F18">
-        <f t="shared" si="0"/>
-        <v>-1.2179562985240696E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1423,12 +1360,8 @@
       <c r="E19">
         <v>8314386</v>
       </c>
-      <c r="F19">
-        <f t="shared" si="0"/>
-        <v>-7.0880844289949486E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1444,12 +1377,8 @@
       <c r="E20">
         <v>8280816</v>
       </c>
-      <c r="F20">
-        <f t="shared" si="0"/>
-        <v>-3.8028741812941545E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -1465,12 +1394,8 @@
       <c r="E21">
         <v>8378236</v>
       </c>
-      <c r="F21">
-        <f t="shared" si="0"/>
-        <v>8.8600575309154533E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -1486,12 +1411,8 @@
       <c r="E22">
         <v>8392014</v>
       </c>
-      <c r="F22">
-        <f t="shared" si="0"/>
-        <v>9.1730852383775669E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -1507,12 +1428,8 @@
       <c r="E23">
         <v>8526316</v>
       </c>
-      <c r="F23">
-        <f t="shared" si="0"/>
-        <v>2.0924456087023308E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -1528,12 +1445,8 @@
       <c r="E24">
         <v>8372067</v>
       </c>
-      <c r="F24">
-        <f t="shared" si="0"/>
-        <v>-1.1478170990387327E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -1549,12 +1462,8 @@
       <c r="E25">
         <v>8400187</v>
       </c>
-      <c r="F25">
-        <f t="shared" si="0"/>
-        <v>1.396477512830693E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -1570,12 +1479,8 @@
       <c r="E26">
         <v>8467555</v>
       </c>
-      <c r="F26">
-        <f t="shared" si="0"/>
-        <v>7.0817712741631312E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -1591,12 +1496,8 @@
       <c r="E27">
         <v>8481490</v>
       </c>
-      <c r="F27">
-        <f t="shared" si="0"/>
-        <v>1.2389403688604726E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -1612,12 +1513,8 @@
       <c r="E28">
         <v>8530831</v>
       </c>
-      <c r="F28">
-        <f t="shared" si="0"/>
-        <v>6.3207364513565593E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -1633,12 +1530,8 @@
       <c r="E29">
         <v>8567007</v>
       </c>
-      <c r="F29">
-        <f t="shared" si="0"/>
-        <v>7.1411363833666121E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -1654,12 +1547,8 @@
       <c r="E30">
         <v>9145313</v>
       </c>
-      <c r="F30">
-        <f t="shared" si="0"/>
-        <v>4.4461087753372742E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -1675,12 +1564,8 @@
       <c r="E31">
         <v>8408740</v>
       </c>
-      <c r="F31">
-        <f t="shared" si="0"/>
-        <v>-5.9493891396677795E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -1696,12 +1581,8 @@
       <c r="E32">
         <v>8279372</v>
       </c>
-      <c r="F32">
-        <f t="shared" si="0"/>
-        <v>-1.2867259192624365E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -1717,12 +1598,8 @@
       <c r="E33">
         <v>8122966</v>
       </c>
-      <c r="F33">
-        <f t="shared" si="0"/>
-        <v>-1.1613813801111698E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -1738,12 +1615,8 @@
       <c r="E34">
         <v>8161748</v>
       </c>
-      <c r="F34">
-        <f t="shared" si="0"/>
-        <v>-4.2622680639840859E-4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -1759,12 +1632,8 @@
       <c r="E35">
         <v>8313411</v>
       </c>
-      <c r="F35">
-        <f t="shared" si="0"/>
-        <v>6.3674861191344405E-3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>10</v>
       </c>
@@ -1780,12 +1649,8 @@
       <c r="E36">
         <v>8462225</v>
       </c>
-      <c r="F36">
-        <f t="shared" si="0"/>
-        <v>1.3387339606788087E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -1801,12 +1666,8 @@
       <c r="E37">
         <v>8493971</v>
       </c>
-      <c r="F37">
-        <f t="shared" si="0"/>
-        <v>2.6779607458868203E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
         <v>10</v>
       </c>
@@ -1822,12 +1683,8 @@
       <c r="E38">
         <v>8419796</v>
       </c>
-      <c r="F38">
-        <f t="shared" si="0"/>
-        <v>-7.196616836677475E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -1843,12 +1700,8 @@
       <c r="E39">
         <v>8375685</v>
       </c>
-      <c r="F39">
-        <f t="shared" si="0"/>
-        <v>-1.7114285836675688E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
         <v>10</v>
       </c>
@@ -1864,12 +1717,8 @@
       <c r="E40">
         <v>8416263</v>
       </c>
-      <c r="F40">
-        <f t="shared" si="0"/>
-        <v>1.9396767055059466E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -1885,12 +1734,8 @@
       <c r="E41">
         <v>8469094</v>
       </c>
-      <c r="F41">
-        <f t="shared" si="0"/>
-        <v>1.034216924014854E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>10</v>
       </c>
@@ -1906,12 +1751,8 @@
       <c r="E42">
         <v>8649792</v>
       </c>
-      <c r="F42">
-        <f t="shared" si="0"/>
-        <v>6.4443993194019736E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1926,10 +1767,6 @@
       </c>
       <c r="E43">
         <v>8979524</v>
-      </c>
-      <c r="F43">
-        <f>(C43-C42)/C42</f>
-        <v>2.7659029078555195E-2</v>
       </c>
     </row>
   </sheetData>
